--- a/diseases/d029/2005-2009.xlsx
+++ b/diseases/d029/2005-2009.xlsx
@@ -36794,7 +36794,7 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN216" t="b">
@@ -38031,7 +38031,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -39268,7 +39268,7 @@
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN230" t="b">
@@ -40505,7 +40505,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -41742,7 +41742,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -42979,7 +42979,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -44216,7 +44216,7 @@
       </c>
       <c r="AM258" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN258" t="b">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -46690,7 +46690,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -47927,7 +47927,7 @@
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -49164,7 +49164,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -50401,7 +50401,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN293" t="b">
